--- a/reports/pdf_rolling5_20261002.xlsx
+++ b/reports/pdf_rolling5_20261002.xlsx
@@ -560,7 +560,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,035억   ·   현금 54억(1.0%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 15종목  /  매도 13종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억   ·   현금 36억(0.7%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 15종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -656,7 +656,7 @@
         <v>150</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2772060846</v>
+        <v>2752319380</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>-244</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-8562719013</v>
+        <v>-8501738884</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>32</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>503296154</v>
+        <v>499711887</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>-79</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-854227261</v>
+        <v>-848143809</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1567885478</v>
+        <v>1556719649</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>-65</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-693899912</v>
+        <v>-688958245</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1512837462</v>
+        <v>1502063661</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>-51</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1476417301</v>
+        <v>-1465902870</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>552052968</v>
+        <v>548121476</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>-34</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-224595909</v>
+        <v>-222996430</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -869,23 +869,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2116203046</v>
+        <v>1658418826</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.54%→0.99%</t>
+          <t>0.40%→0.75%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>36→60</t>
+          <t>34→58</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -897,7 +897,7 @@
         <v>-28</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1409229230</v>
+        <v>-1399193285</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -913,23 +913,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1670314110</v>
+        <v>2101132326</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.40%→0.75%</t>
+          <t>0.54%→0.99%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>34→58</t>
+          <t>36→60</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -941,7 +941,7 @@
         <v>-14</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-322718998</v>
+        <v>-320420728</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>455178289</v>
+        <v>451936698</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>-13</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-366757412</v>
+        <v>-364145518</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>791315242</v>
+        <v>785679823</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-932080884</v>
+        <v>-925442991</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>272192783</v>
+        <v>270254339</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>-9</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-668833404</v>
+        <v>-664070250</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>475772145</v>
+        <v>472383894</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1110,23 +1110,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-669226604</v>
+        <v>-322079927</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.48%</t>
+          <t>0.28%→0.18%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>32→24</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2944085898</v>
+        <v>2923119341</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1154,23 +1154,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-324390099</v>
+        <v>-664460650</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.18%</t>
+          <t>0.64%→0.48%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>32→24</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>508014555</v>
+        <v>504396686</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-657823801</v>
+        <v>-653139053</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>237394572</v>
+        <v>235703947</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>925986283</v>
+        <v>919391793</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,250억   ·   현금 67억(1.9%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억   ·   현금 44억(1.3%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1373,7 +1373,7 @@
         <v>130</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>2957564434</v>
+        <v>2957565000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>-385</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1483986066</v>
+        <v>-1483986350</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>119</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1801760805</v>
+        <v>1801761150</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>-243</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-2096968099</v>
+        <v>-2096968500</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>86</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>2410820339</v>
+        <v>2410820800</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>-70</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-937215821</v>
+        <v>-937216000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>50</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>703434866</v>
+        <v>703435000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>-20</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-999975809</v>
+        <v>-999976000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>43</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1090716291</v>
+        <v>1090716500</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>-19</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-329908337</v>
+        <v>-329908400</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>960227816</v>
+        <v>960228000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>676238871</v>
+        <v>676239000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,723억   ·   현금 131억(4.4%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,868억   ·   현금 87억(3.0%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1666,7 +1666,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,988억   ·   현금 30억(1.4%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 6종목  /  매도 7종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,140억   ·   현금 20억(0.9%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 6종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1762,7 +1762,7 @@
         <v>456</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>7160795207</v>
+        <v>7160794413</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1776,14 +1776,14 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>셀트리온제약  (편출) ※</t>
+          <t>셀트리온제약  (편출)</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-632</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-8852296619</v>
+        <v>-8852295638</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>279</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2940994474</v>
+        <v>2940994148</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>-76</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-2060443372</v>
+        <v>-2060443143</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>217</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2267855899</v>
+        <v>2267855647</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>-60</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-2070695771</v>
+        <v>-2070695541</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>212</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>3463072616</v>
+        <v>3463072233</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>-50</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-3436719619</v>
+        <v>-3436719238</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>65</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>6218224311</v>
+        <v>6218223622</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>-45</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-870731904</v>
+        <v>-870731807</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>31</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>2054667372</v>
+        <v>2054667145</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>-27</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-4849131963</v>
+        <v>-4849131425</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>-12</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-657164327</v>
+        <v>-657164254</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 308억   ·   현금 5억(1.5%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 8종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 326억   ·   현금 3억(1.0%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2143,11 +2143,11 @@
         <v>112</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>36612800</v>
+        <v>38494400</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.73%</t>
+          <t>2.60%→2.72%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2164,11 +2164,11 @@
         <v>-68</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-182784000</v>
+        <v>-191590000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>7.99%→7.40%</t>
+          <t>7.92%→7.35%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2187,11 +2187,11 @@
         <v>111</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>78010800</v>
+        <v>80885700</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>6.94%→7.20%</t>
+          <t>6.81%→7.07%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2208,11 +2208,11 @@
         <v>-33</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-45853500</v>
+        <v>-48741000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>3.82%→3.68%</t>
+          <t>3.84%→3.70%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2231,11 +2231,11 @@
         <v>65</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>91682500</v>
+        <v>99417500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.94%→2.24%</t>
+          <t>1.99%→2.30%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2252,11 +2252,11 @@
         <v>-20</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-88200000</v>
+        <v>-99120000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>3.06%→2.77%</t>
+          <t>3.25%→2.95%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2275,11 +2275,11 @@
         <v>35</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>62842500</v>
+        <v>63822500</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>4.87%→5.08%</t>
+          <t>4.68%→4.88%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2296,11 +2296,11 @@
         <v>-14</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-39543000</v>
+        <v>-41160000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.16%</t>
+          <t>2.26%→2.13%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2312,88 +2312,88 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>57680000</v>
+        <v>81200000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.23%→2.43%</t>
+          <t>3.74%→4.00%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-34314000</v>
+        <v>-77238000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.49%→1.38%</t>
+          <t>3.09%→2.86%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>75320000</v>
+        <v>58380000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>3.66%→3.92%</t>
+          <t>2.14%→2.32%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-70434000</v>
+        <v>-37674000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.75%</t>
+          <t>1.55%→1.43%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         <v>15</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>40057500</v>
+        <v>40215000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>1.10%→1.24%</t>
+          <t>1.05%→1.17%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2428,11 +2428,11 @@
         <v>-5</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-32375000</v>
+        <v>-32795000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.37%→1.27%</t>
+          <t>1.31%→1.21%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2451,11 +2451,11 @@
         <v>9</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>7623000</v>
+        <v>7654500</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.12%→2.15%</t>
+          <t>2.01%→2.04%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 474억   ·   현금 158억(23.9%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 1종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 509억   ·   현금 15억(2.9%)      오늘 2026-10-02  vs  5일전 2026-09-23      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B59" s="4" t="n"/>
@@ -2568,7 +2568,7 @@
         <v>87</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>522182879</v>
+        <v>522182968</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>-58</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-363729724</v>
+        <v>-363729787</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>-10</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-211302072</v>
+        <v>-211302108</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,133억      오늘 2026-10-02  vs  5일전 2026-09-23      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      오늘 2026-10-02  vs  5일전 2026-09-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B65" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261002.xlsx
+++ b/reports/pdf_rolling5_20261002.xlsx
@@ -1110,23 +1110,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-322079927</v>
+        <v>-664460650</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.18%</t>
+          <t>0.64%→0.48%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>32→24</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1154,23 +1154,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-664460650</v>
+        <v>-322079927</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.48%</t>
+          <t>0.28%→0.18%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>32→24</t>
         </is>
       </c>
     </row>
@@ -2312,88 +2312,88 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>81200000</v>
+        <v>58380000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>3.74%→4.00%</t>
+          <t>2.14%→2.32%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-77238000</v>
+        <v>-37674000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.09%→2.86%</t>
+          <t>1.55%→1.43%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>58380000</v>
+        <v>81200000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.14%→2.32%</t>
+          <t>3.74%→4.00%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-37674000</v>
+        <v>-77238000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.43%</t>
+          <t>3.09%→2.86%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261002.xlsx
+++ b/reports/pdf_rolling5_20261002.xlsx
@@ -869,23 +869,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1658418826</v>
+        <v>2101132326</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.40%→0.75%</t>
+          <t>0.54%→0.99%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>34→58</t>
+          <t>36→60</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -913,23 +913,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2101132326</v>
+        <v>1658418826</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.54%→0.99%</t>
+          <t>0.40%→0.75%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>36→60</t>
+          <t>34→58</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1089,88 +1089,88 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>가온칩스</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>472383894</v>
+        <v>2923119341</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.44%→1.47%</t>
+          <t>0.47%→1.05%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>155→165</t>
+          <t>9→19</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-664460650</v>
+        <v>-322079927</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.48%</t>
+          <t>0.28%→0.18%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>32→24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>가온칩스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2923119341</v>
+        <v>472383894</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.47%→1.05%</t>
+          <t>1.44%→1.47%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>9→19</t>
+          <t>155→165</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-322079927</v>
+        <v>-664460650</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.18%</t>
+          <t>0.64%→0.48%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>32→24</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1586,23 +1586,23 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>960228000</v>
+        <v>676239000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>8.39%→8.23%</t>
+          <t>3.61%→3.68%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G30" s="17" t="n"/>
@@ -1614,23 +1614,23 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>676239000</v>
+        <v>960228000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>3.61%→3.68%</t>
+          <t>8.39%→8.23%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G31" s="17" t="n"/>

--- a/reports/pdf_rolling5_20261002.xlsx
+++ b/reports/pdf_rolling5_20261002.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,13 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +100,11 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -122,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -162,6 +172,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-23 ~ 2026-10-02  (최근 5거래일)  ·  캡처 7/7</t>
+          <t>최근 5거래일 변화  ·  2026-09-23 ~ 2026-10-02  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1089,88 +1103,88 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>가온칩스</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2923119341</v>
+        <v>472383894</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.47%→1.05%</t>
+          <t>1.44%→1.47%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>9→19</t>
+          <t>155→165</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-322079927</v>
+        <v>-664460650</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.18%</t>
+          <t>0.64%→0.48%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>32→24</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>가온칩스</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>472383894</v>
+        <v>2923119341</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.44%→1.47%</t>
+          <t>0.47%→1.05%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>155→165</t>
+          <t>9→19</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-664460650</v>
+        <v>-322079927</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.48%</t>
+          <t>0.28%→0.18%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>32→24</t>
         </is>
       </c>
     </row>
@@ -2333,23 +2347,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-37674000</v>
+        <v>-77238000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.43%</t>
+          <t>3.09%→2.86%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2377,23 +2391,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-77238000</v>
+        <v>-37674000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>3.09%→2.86%</t>
+          <t>1.55%→1.43%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2631,31 +2645,24 @@
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      오늘 2026-10-02  vs  5일전 2026-09-23      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="20" t="n"/>
+      <c r="F65" s="20" t="n"/>
+      <c r="G65" s="20" t="n"/>
+      <c r="H65" s="20" t="n"/>
+      <c r="I65" s="20" t="n"/>
+      <c r="J65" s="20" t="n"/>
+      <c r="K65" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A59:K59"/>
@@ -2667,7 +2674,6 @@
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
-    <mergeCell ref="A66:K66"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>

--- a/reports/pdf_rolling5_20261002.xlsx
+++ b/reports/pdf_rolling5_20261002.xlsx
@@ -883,23 +883,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2101132326</v>
+        <v>1658418826</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.54%→0.99%</t>
+          <t>0.40%→0.75%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>36→60</t>
+          <t>34→58</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1658418826</v>
+        <v>2101132326</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.40%→0.75%</t>
+          <t>0.54%→0.99%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>34→58</t>
+          <t>36→60</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-664460650</v>
+        <v>-322079927</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.48%</t>
+          <t>0.28%→0.18%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>32→24</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-322079927</v>
+        <v>-664460650</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.18%</t>
+          <t>0.64%→0.48%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>32→24</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1600,23 +1600,23 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>676239000</v>
+        <v>960228000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>3.61%→3.68%</t>
+          <t>8.39%→8.23%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G30" s="17" t="n"/>
@@ -1628,23 +1628,23 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>960228000</v>
+        <v>676239000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>8.39%→8.23%</t>
+          <t>3.61%→3.68%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G31" s="17" t="n"/>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-77238000</v>
+        <v>-37674000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.09%→2.86%</t>
+          <t>1.55%→1.43%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2391,23 +2391,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-37674000</v>
+        <v>-77238000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.43%</t>
+          <t>3.09%→2.86%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
